--- a/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
+++ b/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
@@ -492,16 +492,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.84</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -570,13 +573,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>93.55</v>
       </c>
       <c r="H5">
         <v>8.1</v>
@@ -710,16 +713,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -733,16 +739,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -756,16 +765,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H4">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -779,16 +791,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -802,16 +817,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>97.37</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -825,16 +843,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H7">
+        <v>9.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -848,16 +869,19 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H8">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -910,16 +934,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -936,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>96.55</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -971,7 +998,7 @@
         <v>97.62</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -988,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>83.87</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1040,16 +1067,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>97.37</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1066,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>97.37</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
+++ b/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="93">
   <si>
     <t>Mat</t>
   </si>
@@ -92,6 +92,210 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MERINO</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>GALVAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>SHERLIN</t>
+  </si>
+  <si>
+    <t>VALENTINA</t>
+  </si>
+  <si>
+    <t>DYLAN OSMAR</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>SAUL AZAEL</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>ISAAC JOHAMET</t>
+  </si>
+  <si>
+    <t>CHRISTOPHER ANDRUS</t>
   </si>
 </sst>
 </file>
@@ -937,16 +1141,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>84.20999999999999</v>
+        <v>97.37</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -963,16 +1167,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>93.09999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1015,16 +1219,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1041,16 +1245,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>97.37</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1076,7 +1280,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1102,7 +1306,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H8">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1142,6 +1346,650 @@
         <v>24</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920003</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920015</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920017</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920382</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920038</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920002</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920004</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920005</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920013</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920014</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920016</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920320</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920018</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920012</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920020</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920022</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920322</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920023</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920024</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920025</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920326</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920026</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920173</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920330</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920027</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920031</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
+++ b/docentes/Faltante Faltante Faltante - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="96">
   <si>
     <t>Mat</t>
   </si>
@@ -97,39 +97,42 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MERINO</t>
   </si>
   <si>
@@ -160,48 +163,51 @@
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>QUERO</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>MACARIO</t>
   </si>
   <si>
@@ -223,46 +229,49 @@
     <t>DANIEL</t>
   </si>
   <si>
+    <t>EDER</t>
+  </si>
+  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>RUBEN DE JESUS</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS YAEL</t>
+  </si>
+  <si>
+    <t>GABAEL</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
     <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
   </si>
   <si>
     <t>CESAR</t>
@@ -1316,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1354,10 +1363,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1371,16 +1380,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1394,16 +1403,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1417,16 +1426,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920382</v>
+        <v>22330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1446,10 +1455,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1469,10 +1478,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1492,10 +1501,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1515,10 +1524,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1538,10 +1547,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1561,10 +1570,10 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1581,13 +1590,13 @@
         <v>22330051920014</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1607,10 +1616,10 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1630,10 +1639,10 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1653,10 +1662,10 @@
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1676,10 +1685,10 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1696,13 +1705,13 @@
         <v>22330051920020</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1716,16 +1725,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920022</v>
+        <v>22330051920382</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1739,16 +1748,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920322</v>
+        <v>22330051920022</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1762,16 +1771,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920023</v>
+        <v>22330051920322</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1785,16 +1794,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920024</v>
+        <v>22330051920023</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1808,16 +1817,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920025</v>
+        <v>22330051920024</v>
       </c>
       <c r="B22" t="s">
         <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -1831,16 +1840,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920326</v>
+        <v>22330051920025</v>
       </c>
       <c r="B23" t="s">
         <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1854,16 +1863,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920026</v>
+        <v>22330051920326</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1877,16 +1886,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920173</v>
+        <v>22330051920026</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1900,16 +1909,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920330</v>
+        <v>22330051920173</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -1923,16 +1932,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920027</v>
+        <v>22330051920330</v>
       </c>
       <c r="B27" t="s">
         <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -1946,16 +1955,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920332</v>
+        <v>22330051920027</v>
       </c>
       <c r="B28" t="s">
         <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -1969,24 +1978,47 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920031</v>
+        <v>22330051920332</v>
       </c>
       <c r="B29" t="s">
         <v>45</v>
       </c>
       <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920031</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
         <v>35</v>
       </c>
-      <c r="D29" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="D30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
         <v>17</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>1</v>
       </c>
     </row>
